--- a/gauss_results.xlsx
+++ b/gauss_results.xlsx
@@ -495,37 +495,37 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>30.60223188646952</v>
+        <v>31.96107038592699</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>621.7212141418541</v>
+        <v>655.6603886255492</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>333.7045951215126</v>
+        <v>341.2114516483439</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>566.7442010537546</v>
+        <v>580.1074963992396</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>81.5062999769999</v>
+        <v>81.5209322099554</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>365.5400076794413</v>
+        <v>374.8639851575085</v>
       </c>
     </row>
     <row r="3">
@@ -533,37 +533,37 @@
         <v>0.2015</v>
       </c>
       <c r="B3" t="n">
-        <v>30.87919519524829</v>
+        <v>30.91059293958557</v>
       </c>
       <c r="C3" t="n">
         <v>0.31</v>
       </c>
       <c r="D3" t="n">
-        <v>631.9934114429628</v>
+        <v>630.35141594392</v>
       </c>
       <c r="E3" t="n">
         <v>0.217</v>
       </c>
       <c r="F3" t="n">
-        <v>330.0068834322834</v>
+        <v>330.2032627102528</v>
       </c>
       <c r="G3" t="n">
         <v>0.248</v>
       </c>
       <c r="H3" t="n">
-        <v>557.1768055465363</v>
+        <v>556.0443950361438</v>
       </c>
       <c r="I3" t="n">
         <v>0.2635</v>
       </c>
       <c r="J3" t="n">
-        <v>78.35030419629942</v>
+        <v>78.34937132292869</v>
       </c>
       <c r="K3" t="n">
         <v>0.31</v>
       </c>
       <c r="L3" t="n">
-        <v>359.5170860773202</v>
+        <v>358.3045977140816</v>
       </c>
     </row>
     <row r="4">
@@ -571,37 +571,37 @@
         <v>0.403</v>
       </c>
       <c r="B4" t="n">
-        <v>28.68168775932779</v>
+        <v>27.96181752311704</v>
       </c>
       <c r="C4" t="n">
         <v>0.62</v>
       </c>
       <c r="D4" t="n">
-        <v>580.4281217346308</v>
+        <v>560.1367800263656</v>
       </c>
       <c r="E4" t="n">
         <v>0.434</v>
       </c>
       <c r="F4" t="n">
-        <v>303.2062984012458</v>
+        <v>299.2641164379688</v>
       </c>
       <c r="G4" t="n">
         <v>0.496</v>
       </c>
       <c r="H4" t="n">
-        <v>497.8799922147849</v>
+        <v>489.6800790823431</v>
       </c>
       <c r="I4" t="n">
         <v>0.527</v>
       </c>
       <c r="J4" t="n">
-        <v>69.56471820872484</v>
+        <v>69.5560085640126</v>
       </c>
       <c r="K4" t="n">
         <v>0.6355</v>
       </c>
       <c r="L4" t="n">
-        <v>316.2195451529607</v>
+        <v>310.0380879198034</v>
       </c>
     </row>
     <row r="5">
@@ -609,37 +609,37 @@
         <v>0.6045</v>
       </c>
       <c r="B5" t="n">
-        <v>24.5227569655217</v>
+        <v>23.65895178996782</v>
       </c>
       <c r="C5" t="n">
         <v>0.9455</v>
       </c>
       <c r="D5" t="n">
-        <v>475.8762082659721</v>
+        <v>454.6125444839989</v>
       </c>
       <c r="E5" t="n">
         <v>0.6665</v>
       </c>
       <c r="F5" t="n">
-        <v>255.1973299968838</v>
+        <v>250.4188249568323</v>
       </c>
       <c r="G5" t="n">
         <v>0.744</v>
       </c>
       <c r="H5" t="n">
-        <v>404.3728790277241</v>
+        <v>396.2026585481264</v>
       </c>
       <c r="I5" t="n">
         <v>0.806</v>
       </c>
       <c r="J5" t="n">
-        <v>56.24630073301275</v>
+        <v>56.2372997268971</v>
       </c>
       <c r="K5" t="n">
         <v>0.9455</v>
       </c>
       <c r="L5" t="n">
-        <v>251.7967602643607</v>
+        <v>246.2329861855991</v>
       </c>
     </row>
     <row r="6">
@@ -647,37 +647,37 @@
         <v>0.806</v>
       </c>
       <c r="B6" t="n">
-        <v>19.30010821952657</v>
+        <v>18.72395730749189</v>
       </c>
       <c r="C6" t="n">
         <v>1.2555</v>
       </c>
       <c r="D6" t="n">
-        <v>354.947319359092</v>
+        <v>343.7623388409334</v>
       </c>
       <c r="E6" t="n">
         <v>0.8835</v>
       </c>
       <c r="F6" t="n">
-        <v>201.3345620095454</v>
+        <v>198.1238233064115</v>
       </c>
       <c r="G6" t="n">
         <v>0.992</v>
       </c>
       <c r="H6" t="n">
-        <v>298.5142496714259</v>
+        <v>294.5264573341436</v>
       </c>
       <c r="I6" t="n">
         <v>1.0695</v>
       </c>
       <c r="J6" t="n">
-        <v>42.40435847638349</v>
+        <v>42.39958696646719</v>
       </c>
       <c r="K6" t="n">
         <v>1.271</v>
       </c>
       <c r="L6" t="n">
-        <v>177.4230181946825</v>
+        <v>175.4038193818084</v>
       </c>
     </row>
     <row r="7">
@@ -685,37 +685,37 @@
         <v>1.0075</v>
       </c>
       <c r="B7" t="n">
-        <v>13.98221751599811</v>
+        <v>13.86027432455522</v>
       </c>
       <c r="C7" t="n">
         <v>1.5655</v>
       </c>
       <c r="D7" t="n">
-        <v>239.195408864422</v>
+        <v>240.2607051814871</v>
       </c>
       <c r="E7" t="n">
         <v>1.116</v>
       </c>
       <c r="F7" t="n">
-        <v>143.9317435969835</v>
+        <v>143.32796338498</v>
       </c>
       <c r="G7" t="n">
         <v>1.2555</v>
       </c>
       <c r="H7" t="n">
-        <v>194.7448742062695</v>
+        <v>195.8673144636948</v>
       </c>
       <c r="I7" t="n">
         <v>1.333</v>
       </c>
       <c r="J7" t="n">
-        <v>29.52744470101762</v>
+        <v>29.52783122438595</v>
       </c>
       <c r="K7" t="n">
         <v>1.581</v>
       </c>
       <c r="L7" t="n">
-        <v>114.3795019296081</v>
+        <v>115.7504657056349</v>
       </c>
     </row>
     <row r="8">
@@ -723,37 +723,37 @@
         <v>1.209</v>
       </c>
       <c r="B8" t="n">
-        <v>9.324342626951873</v>
+        <v>9.596614526738549</v>
       </c>
       <c r="C8" t="n">
         <v>1.891</v>
       </c>
       <c r="D8" t="n">
-        <v>141.6866989730725</v>
+        <v>151.5405367535298</v>
       </c>
       <c r="E8" t="n">
         <v>1.333</v>
       </c>
       <c r="F8" t="n">
-        <v>97.50475214199965</v>
+        <v>98.99131608887096</v>
       </c>
       <c r="G8" t="n">
         <v>1.5035</v>
       </c>
       <c r="H8" t="n">
-        <v>118.0615120363228</v>
+        <v>122.2567874674006</v>
       </c>
       <c r="I8" t="n">
         <v>1.612</v>
       </c>
       <c r="J8" t="n">
-        <v>18.45822779498598</v>
+        <v>18.46249651746389</v>
       </c>
       <c r="K8" t="n">
         <v>1.9065</v>
       </c>
       <c r="L8" t="n">
-        <v>64.56522611626274</v>
+        <v>67.88060521393922</v>
       </c>
     </row>
     <row r="9">
@@ -761,37 +761,37 @@
         <v>1.4105</v>
       </c>
       <c r="B9" t="n">
-        <v>5.723823753741303</v>
+        <v>6.214931066751012</v>
       </c>
       <c r="C9" t="n">
         <v>2.201</v>
       </c>
       <c r="D9" t="n">
-        <v>77.54468464031504</v>
+        <v>90.12780524406172</v>
       </c>
       <c r="E9" t="n">
         <v>1.5655</v>
       </c>
       <c r="F9" t="n">
-        <v>59.20581712281493</v>
+        <v>61.9117713189154</v>
       </c>
       <c r="G9" t="n">
         <v>1.7515</v>
       </c>
       <c r="H9" t="n">
-        <v>65.05435082596019</v>
+        <v>70.11096909405161</v>
       </c>
       <c r="I9" t="n">
         <v>1.8755</v>
       </c>
       <c r="J9" t="n">
-        <v>10.91373887035488</v>
+        <v>10.91939007008308</v>
       </c>
       <c r="K9" t="n">
         <v>2.2165</v>
       </c>
       <c r="L9" t="n">
-        <v>33.69874477269451</v>
+        <v>37.22047626785249</v>
       </c>
     </row>
     <row r="10">
@@ -799,37 +799,37 @@
         <v>1.612</v>
       </c>
       <c r="B10" t="n">
-        <v>3.234298813584005</v>
+        <v>3.764667477919017</v>
       </c>
       <c r="C10" t="n">
         <v>2.511</v>
       </c>
       <c r="D10" t="n">
-        <v>38.34369988726775</v>
+        <v>49.54460171925878</v>
       </c>
       <c r="E10" t="n">
         <v>1.7825</v>
       </c>
       <c r="F10" t="n">
-        <v>34.43979547703449</v>
+        <v>37.32809609776969</v>
       </c>
       <c r="G10" t="n">
         <v>1.9995</v>
       </c>
       <c r="H10" t="n">
-        <v>32.58142349294114</v>
+        <v>36.94034439110316</v>
       </c>
       <c r="I10" t="n">
         <v>2.139</v>
       </c>
       <c r="J10" t="n">
-        <v>5.960132987434429</v>
+        <v>5.965393435616407</v>
       </c>
       <c r="K10" t="n">
         <v>2.542</v>
       </c>
       <c r="L10" t="n">
-        <v>15.23894318796172</v>
+        <v>17.96946014054209</v>
       </c>
     </row>
     <row r="11">
@@ -837,37 +837,37 @@
         <v>1.8135</v>
       </c>
       <c r="B11" t="n">
-        <v>1.682286229335385</v>
+        <v>2.132990736691313</v>
       </c>
       <c r="C11" t="n">
         <v>2.8365</v>
       </c>
       <c r="D11" t="n">
-        <v>16.40971186742115</v>
+        <v>24.2851709068226</v>
       </c>
       <c r="E11" t="n">
         <v>2.015</v>
       </c>
       <c r="F11" t="n">
-        <v>17.76231243267586</v>
+        <v>20.18337886428932</v>
       </c>
       <c r="G11" t="n">
         <v>2.263</v>
       </c>
       <c r="H11" t="n">
-        <v>14.07508738999201</v>
+        <v>17.04132619246084</v>
       </c>
       <c r="I11" t="n">
         <v>2.418</v>
       </c>
       <c r="J11" t="n">
-        <v>2.880575674485509</v>
+        <v>2.884476717276057</v>
       </c>
       <c r="K11" t="n">
         <v>2.8675</v>
       </c>
       <c r="L11" t="n">
-        <v>6.151298418421204</v>
+        <v>7.852773764134719</v>
       </c>
     </row>
   </sheetData>

--- a/gauss_results.xlsx
+++ b/gauss_results.xlsx
@@ -425,18 +425,28 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Radius_1</t>
+          <t>Radius_left_1</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Line_1</t>
+          <t>Line_left_1</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Radius_right_1</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Line_right_1</t>
         </is>
       </c>
     </row>
@@ -445,79 +455,139 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>43.37786087351307</v>
+        <v>643.4793667555185</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" t="n">
+        <v>655.5222045489891</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.4185</v>
+        <v>0.372</v>
       </c>
       <c r="B3" t="n">
-        <v>41.83405902315604</v>
+        <v>615.9481639979953</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.2945</v>
+      </c>
+      <c r="D3" t="n">
+        <v>632.6457742210114</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0.837</v>
+        <v>0.7285</v>
       </c>
       <c r="B4" t="n">
-        <v>37.52456139804661</v>
+        <v>544.1327804097961</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.6045</v>
+      </c>
+      <c r="D4" t="n">
+        <v>564.4035601721454</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>1.2555</v>
+        <v>1.085</v>
       </c>
       <c r="B5" t="n">
-        <v>31.30581332841536</v>
+        <v>443.5921288167148</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.9145</v>
+      </c>
+      <c r="D5" t="n">
+        <v>465.4061017202801</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>1.674</v>
+        <v>1.457</v>
       </c>
       <c r="B6" t="n">
-        <v>24.29171093274496</v>
+        <v>329.0149885234547</v>
+      </c>
+      <c r="C6" t="n">
+        <v>1.2245</v>
+      </c>
+      <c r="D6" t="n">
+        <v>354.7215686336112</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>2.0925</v>
+        <v>1.8135</v>
       </c>
       <c r="B7" t="n">
-        <v>17.53133401635053</v>
+        <v>227.622116610106</v>
+      </c>
+      <c r="C7" t="n">
+        <v>1.5345</v>
+      </c>
+      <c r="D7" t="n">
+        <v>249.8942797678206</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>2.511</v>
+        <v>2.17</v>
       </c>
       <c r="B8" t="n">
-        <v>11.76780790994249</v>
+        <v>145.3220273930425</v>
+      </c>
+      <c r="C8" t="n">
+        <v>1.8445</v>
+      </c>
+      <c r="D8" t="n">
+        <v>162.7189858619063</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>2.9295</v>
+        <v>2.542</v>
       </c>
       <c r="B9" t="n">
-        <v>7.346828865511843</v>
+        <v>83.51906277355262</v>
+      </c>
+      <c r="C9" t="n">
+        <v>2.1545</v>
+      </c>
+      <c r="D9" t="n">
+        <v>97.93396501363821</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>3.348</v>
+        <v>2.8985</v>
       </c>
       <c r="B10" t="n">
-        <v>4.266070451700012</v>
+        <v>45.25040139407444</v>
+      </c>
+      <c r="C10" t="n">
+        <v>2.4645</v>
+      </c>
+      <c r="D10" t="n">
+        <v>54.48056994631511</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>3.782</v>
+        <v>3.255</v>
       </c>
       <c r="B11" t="n">
-        <v>2.24887955620676</v>
+        <v>22.6244211236186</v>
+      </c>
+      <c r="C11" t="n">
+        <v>2.7745</v>
+      </c>
+      <c r="D11" t="n">
+        <v>28.01322708345424</v>
       </c>
     </row>
   </sheetData>
